--- a/artfynd/A 538-2024 artfynd.xlsx
+++ b/artfynd/A 538-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 538-2024 artfynd.xlsx
+++ b/artfynd/A 538-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>81745682</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388556.8881795157</v>
+        <v>388557</v>
       </c>
       <c r="R2" t="n">
-        <v>6656092.852893045</v>
+        <v>6656093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81745725</v>
+        <v>81745696</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388549.0179326421</v>
+        <v>388509</v>
       </c>
       <c r="R3" t="n">
-        <v>6656081.088142272</v>
+        <v>6656094</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81745696</v>
+        <v>81745725</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388508.8250829284</v>
+        <v>388549</v>
       </c>
       <c r="R4" t="n">
-        <v>6656093.80688733</v>
+        <v>6656081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
